--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,59 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121241383</v>
+        <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>92692</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1958</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hucksjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546004</v>
+        <v>545956</v>
       </c>
       <c r="R2" t="n">
-        <v>6968289</v>
+        <v>6968158</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,83 +769,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241383</t>
+          <t>https://artportalen.se/Sighting/136722339</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121241438</v>
+        <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>92692</v>
+        <v>97583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1958</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hucksjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545999</v>
+        <v>546014</v>
       </c>
       <c r="R3" t="n">
-        <v>6968267</v>
+        <v>6968179</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,81 +881,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241438</t>
+          <t>https://artportalen.se/Sighting/136722342</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96790327</v>
+        <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Hucksjön, S väg, Jmt</t>
+          <t>Hucksjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546133</v>
+        <v>546115</v>
       </c>
       <c r="R4" t="n">
-        <v>6968240</v>
+        <v>6968149</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,89 +995,69 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>130-årig tallskog på morän</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96790327</t>
+          <t>https://artportalen.se/Sighting/136722345</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121241462</v>
+        <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>93213</v>
+        <v>79506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hucksjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546039</v>
+        <v>546051</v>
       </c>
       <c r="R5" t="n">
-        <v>6968255</v>
+        <v>6968227</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,34 +1105,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241462</t>
+          <t>https://artportalen.se/Sighting/136722350</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121241498</v>
+        <v>121241383</v>
       </c>
       <c r="B6" t="n">
-        <v>93213</v>
+        <v>92692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,25 +1139,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1180,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546092</v>
+        <v>546004</v>
       </c>
       <c r="R6" t="n">
-        <v>6968269</v>
+        <v>6968289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,38 +1236,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241498</t>
+          <t>https://artportalen.se/Sighting/121241383</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121241377</v>
+        <v>121241438</v>
       </c>
       <c r="B7" t="n">
-        <v>87325</v>
+        <v>92692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3690</v>
+        <v>1958</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1294,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546000</v>
+        <v>545999</v>
       </c>
       <c r="R7" t="n">
-        <v>6968294</v>
+        <v>6968267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,38 +1350,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241377</t>
+          <t>https://artportalen.se/Sighting/121241438</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121241415</v>
+        <v>96790327</v>
       </c>
       <c r="B8" t="n">
-        <v>87325</v>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1400,18 +1394,16 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hucksjön, Jmt</t>
+          <t>Norr om Hucksjön, S väg, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546005</v>
+        <v>546133</v>
       </c>
       <c r="R8" t="n">
-        <v>6968272</v>
+        <v>6968240</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,12 +1430,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,56 +1444,64 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>130-årig tallskog på morän</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241415</t>
+          <t>https://artportalen.se/Sighting/96790327</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241494</v>
+        <v>121241462</v>
       </c>
       <c r="B9" t="n">
-        <v>87325</v>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>546092</v>
+        <v>546039</v>
       </c>
       <c r="R9" t="n">
-        <v>6968269</v>
+        <v>6968255</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,50 +1584,42 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241494</t>
+          <t>https://artportalen.se/Sighting/121241462</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121241522</v>
+        <v>121241498</v>
       </c>
       <c r="B10" t="n">
-        <v>87325</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3690</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Soop</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1636,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546111</v>
+        <v>546092</v>
       </c>
       <c r="R10" t="n">
-        <v>6968281</v>
+        <v>6968269</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,65 +1690,54 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241522</t>
+          <t>https://artportalen.se/Sighting/121241498</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121241404</v>
+        <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>93189</v>
+        <v>96558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hucksjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546004</v>
+        <v>546116</v>
       </c>
       <c r="R11" t="n">
-        <v>6968285</v>
+        <v>6968153</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,12 +1761,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,83 +1785,71 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241404</t>
+          <t>https://artportalen.se/Sighting/136722346</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121241469</v>
+        <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>93189</v>
+        <v>91882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hucksjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546023</v>
+        <v>545940</v>
       </c>
       <c r="R12" t="n">
-        <v>6968243</v>
+        <v>6968229</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1894,12 +1873,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,34 +1897,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241469</t>
+          <t>https://artportalen.se/Sighting/136722337</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121241471</v>
+        <v>121241377</v>
       </c>
       <c r="B13" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,21 +1931,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1978,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546043</v>
+        <v>546000</v>
       </c>
       <c r="R13" t="n">
-        <v>6968242</v>
+        <v>6968294</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,16 +2028,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241471</t>
+          <t>https://artportalen.se/Sighting/121241377</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121241486</v>
+        <v>121241415</v>
       </c>
       <c r="B14" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2092,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546078</v>
+        <v>546005</v>
       </c>
       <c r="R14" t="n">
-        <v>6968269</v>
+        <v>6968272</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,16 +2142,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241486</t>
+          <t>https://artportalen.se/Sighting/121241415</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121241518</v>
+        <v>121241494</v>
       </c>
       <c r="B15" t="n">
-        <v>93189</v>
+        <v>87325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,21 +2159,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2206,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546109</v>
+        <v>546092</v>
       </c>
       <c r="R15" t="n">
-        <v>6968278</v>
+        <v>6968269</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,16 +2256,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241518</t>
+          <t>https://artportalen.se/Sighting/121241494</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121241421</v>
+        <v>121241522</v>
       </c>
       <c r="B16" t="n">
-        <v>93191</v>
+        <v>87325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,21 +2273,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2320,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545999</v>
+        <v>546111</v>
       </c>
       <c r="R16" t="n">
-        <v>6968267</v>
+        <v>6968281</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,16 +2370,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241421</t>
+          <t>https://artportalen.se/Sighting/121241522</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121241369</v>
+        <v>121241404</v>
       </c>
       <c r="B17" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,21 +2387,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2434,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545996</v>
+        <v>546004</v>
       </c>
       <c r="R17" t="n">
-        <v>6968298</v>
+        <v>6968285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,16 +2484,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241369</t>
+          <t>https://artportalen.se/Sighting/121241404</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121241510</v>
+        <v>121241469</v>
       </c>
       <c r="B18" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,21 +2501,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2548,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546108</v>
+        <v>546023</v>
       </c>
       <c r="R18" t="n">
-        <v>6968266</v>
+        <v>6968243</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,16 +2598,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241510</t>
+          <t>https://artportalen.se/Sighting/121241469</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121241410</v>
+        <v>121241471</v>
       </c>
       <c r="B19" t="n">
-        <v>91402</v>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2662,10 +2650,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>546008</v>
+        <v>546043</v>
       </c>
       <c r="R19" t="n">
-        <v>6968282</v>
+        <v>6968242</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,16 +2712,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241410</t>
+          <t>https://artportalen.se/Sighting/121241471</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121241501</v>
+        <v>121241486</v>
       </c>
       <c r="B20" t="n">
-        <v>91402</v>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,25 +2729,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2768,7 +2764,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>546092</v>
+        <v>546078</v>
       </c>
       <c r="R20" t="n">
         <v>6968269</v>
@@ -2830,7 +2826,1965 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/121241486</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121241518</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>546109</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6968278</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241518</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136722341</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93396</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>546008</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6968191</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722341</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121241421</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>545999</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6968267</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241421</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121241369</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>545996</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6968298</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241369</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121241510</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>546108</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6968266</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241510</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136722338</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>545910</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6968201</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722338</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136722347</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>546110</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6968185</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722347</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136722348</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>546165</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6968243</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722348</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136722340</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93416</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>545999</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6968188</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722340</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136722333</v>
+      </c>
+      <c r="B30" t="n">
+        <v>89334</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>545965</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6968252</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722333</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136722349</v>
+      </c>
+      <c r="B31" t="n">
+        <v>89334</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>546162</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6968250</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722349</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136722335</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>545963</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6968251</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722335</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136722336</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83461</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>545940</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6968231</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722336</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136722344</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>546107</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6968154</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sandig barrskog, kalkpåverkad</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722344</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121241410</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>546008</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6968282</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241410</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121241501</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>546092</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6968269</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/121241501</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136722331</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hucksjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>545982</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6968298</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Torr sandmark, renlav och lingon/blåbär. Något bedagad. Endast svag läderdoft, frisk. Svag beska.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136722331</t>
         </is>
       </c>
     </row>
@@ -2855,6 +4809,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>136722344</v>
       </c>
       <c r="B34" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>136722344</v>
       </c>
       <c r="B34" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>136722344</v>
       </c>
       <c r="B34" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136722350</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89373</v>
+        <v>89383</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89373</v>
+        <v>89383</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>136722335</v>
       </c>
       <c r="B32" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>136722336</v>
       </c>
       <c r="B33" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>136722344</v>
       </c>
       <c r="B34" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 40818-2024 artfynd.xlsx
+++ b/artfynd/A 40818-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722339</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722342</v>
       </c>
       <c r="B3" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722345</v>
       </c>
       <c r="B4" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136722346</v>
       </c>
       <c r="B11" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>136722337</v>
       </c>
       <c r="B12" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>136722341</v>
       </c>
       <c r="B22" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>136722338</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136722347</v>
       </c>
       <c r="B27" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>136722348</v>
       </c>
       <c r="B28" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136722340</v>
       </c>
       <c r="B29" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136722333</v>
       </c>
       <c r="B30" t="n">
-        <v>89383</v>
+        <v>89384</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136722349</v>
       </c>
       <c r="B31" t="n">
-        <v>89383</v>
+        <v>89384</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136722331</v>
       </c>
       <c r="B37" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
